--- a/data/trans_orig/IP07A08-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07A08-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse alegre en 2007 (tasa de respuesta: 99,6%)</t>
+          <t>Menores según la frecuencia de sentirse alegre, percibida por el adulto en 2007 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>60555</t>
+          <t>60673</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>79176</t>
+          <t>79013</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>63687</t>
+          <t>64127</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>83064</t>
+          <t>83282</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>130121</t>
+          <t>130555</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>156443</t>
+          <t>157084</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>58,52%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43733</t>
+          <t>44457</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62784</t>
+          <t>62298</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53001</t>
+          <t>53250</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>71763</t>
+          <t>70926</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>102529</t>
+          <t>101708</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>128899</t>
+          <t>127779</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>47,61%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7357</t>
+          <t>7524</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2546</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9807</t>
+          <t>9274</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5054</t>
+          <t>4649</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14719</t>
+          <t>13925</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4006</t>
+          <t>3230</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4045</t>
+          <t>4020</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>4511</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4895</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>90770</t>
+          <t>91757</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>113365</t>
+          <t>115179</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>102026</t>
+          <t>101987</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>124389</t>
+          <t>124997</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>201077</t>
+          <t>198147</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>233133</t>
+          <t>231616</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,17%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69200</t>
+          <t>67847</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>90953</t>
+          <t>91023</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67457</t>
+          <t>66573</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90270</t>
+          <t>88799</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>140762</t>
+          <t>143417</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>171874</t>
+          <t>173755</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,64%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5707</t>
+          <t>5547</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15765</t>
+          <t>15027</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6950</t>
+          <t>6539</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17419</t>
+          <t>17236</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14758</t>
+          <t>14772</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>30066</t>
+          <t>29176</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3415</t>
+          <t>3465</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4609</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>680</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5435</t>
+          <t>5917</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4896</t>
+          <t>4429</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4061</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>156476</t>
+          <t>157380</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>186549</t>
+          <t>187675</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>173491</t>
+          <t>171764</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>203150</t>
+          <t>201130</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>338134</t>
+          <t>338003</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>380208</t>
+          <t>378401</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>56,77%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>118213</t>
+          <t>117367</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>146656</t>
+          <t>148109</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>125050</t>
+          <t>125080</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>154384</t>
+          <t>154784</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>252198</t>
+          <t>253439</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>293464</t>
+          <t>294176</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,13%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8031</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19664</t>
+          <t>19198</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10789</t>
+          <t>10637</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23945</t>
+          <t>23672</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>22024</t>
+          <t>21278</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>38703</t>
+          <t>38267</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3442</t>
+          <t>3425</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>682</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6423</t>
+          <t>6039</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>805</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7481</t>
+          <t>7854</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5573</t>
+          <t>5581</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>649</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5546</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse alegre en 2012 (tasa de respuesta: 98,12%)</t>
+          <t>Menores según la frecuencia de sentirse alegre, percibida por el adulto en 2012 (tasa de respuesta: 98,12%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>87521</t>
+          <t>88269</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>107922</t>
+          <t>108282</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>77714</t>
+          <t>75764</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>96951</t>
+          <t>96254</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>171535</t>
+          <t>171187</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>199433</t>
+          <t>199100</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>63,92%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43919</t>
+          <t>42877</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63359</t>
+          <t>62545</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50181</t>
+          <t>51328</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69848</t>
+          <t>71355</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99383</t>
+          <t>99363</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>128064</t>
+          <t>128169</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,15%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>657</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6919</t>
+          <t>7038</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3463</t>
+          <t>3449</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12281</t>
+          <t>11777</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5283</t>
+          <t>5426</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15294</t>
+          <t>15754</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3404</t>
+          <t>3840</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4562</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>621</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6185</t>
+          <t>5553</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3785</t>
+          <t>3139</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80657</t>
+          <t>81074</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>102380</t>
+          <t>101709</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>91367</t>
+          <t>91021</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>111702</t>
+          <t>112932</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>178837</t>
+          <t>178246</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>208653</t>
+          <t>207922</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>60,63%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57885</t>
+          <t>58794</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>78820</t>
+          <t>78645</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57266</t>
+          <t>56448</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>76769</t>
+          <t>76927</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>119720</t>
+          <t>120750</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>149748</t>
+          <t>149409</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>43,56%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2199</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10562</t>
+          <t>9990</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>2203</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10471</t>
+          <t>9894</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6180</t>
+          <t>5891</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17185</t>
+          <t>17447</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4688</t>
+          <t>5310</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3700</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>658</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6752</t>
+          <t>6581</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3129</t>
+          <t>3319</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4843</t>
+          <t>4565</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t>5214</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>175415</t>
+          <t>176647</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>204360</t>
+          <t>205297</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>174190</t>
+          <t>173078</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>202715</t>
+          <t>202939</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4422,47 +4422,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
+          <t>61,03%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>378656</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>357244</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>399052</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>57,86%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>54,59%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>60,97%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>548</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>378656</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>358158</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>398169</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>57,86%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>54,73%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>60,84%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>107566</t>
+          <t>106485</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>134727</t>
+          <t>135861</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>113575</t>
+          <t>112876</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>142749</t>
+          <t>141458</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>229339</t>
+          <t>228213</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>267692</t>
+          <t>269308</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>41,15%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4153</t>
+          <t>4471</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12639</t>
+          <t>13748</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7334</t>
+          <t>7347</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18771</t>
+          <t>19014</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13150</t>
+          <t>13449</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>27865</t>
+          <t>28805</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -4716,7 +4716,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6365</t>
+          <t>6061</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>686</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5873</t>
+          <t>6229</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9827</t>
+          <t>9660</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>3787</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>611</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>6302</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>664</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6534</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse alegre en 2016 (tasa de respuesta: 99,02%)</t>
+          <t>Menores según la frecuencia de sentirse alegre, percibida por el adulto en 2016 (tasa de respuesta: 99,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>95892</t>
+          <t>95255</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>117519</t>
+          <t>117742</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>99380</t>
+          <t>98936</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>121304</t>
+          <t>122419</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>200369</t>
+          <t>200629</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>232041</t>
+          <t>231952</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>62,14%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61641</t>
+          <t>61222</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82985</t>
+          <t>83572</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58719</t>
+          <t>58031</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80452</t>
+          <t>81596</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>127531</t>
+          <t>126773</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>159731</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,79%</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3159</t>
+          <t>3327</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12328</t>
+          <t>11669</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2232</t>
+          <t>2697</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9924</t>
+          <t>10452</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7355</t>
+          <t>7136</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18662</t>
+          <t>18223</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>4914</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4886</t>
+          <t>4437</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>72044</t>
+          <t>73371</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>94687</t>
+          <t>95495</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79785</t>
+          <t>79330</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>101834</t>
+          <t>101214</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>159823</t>
+          <t>159459</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>191342</t>
+          <t>189934</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,08%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62625</t>
+          <t>62290</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>84676</t>
+          <t>83078</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64762</t>
+          <t>65775</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>87868</t>
+          <t>87603</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>134386</t>
+          <t>135844</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>165817</t>
+          <t>166477</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>48,28%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5649</t>
+          <t>5602</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15443</t>
+          <t>16198</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2865</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12075</t>
+          <t>11428</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>10901</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>23305</t>
+          <t>23520</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4931</t>
+          <t>4795</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3611</t>
+          <t>4278</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5532</t>
+          <t>6205</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -6418,12 +6418,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>656</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5625</t>
+          <t>5775</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>665</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6338</t>
+          <t>6262</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>173857</t>
+          <t>173862</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>204970</t>
+          <t>207589</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>185330</t>
+          <t>185167</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>217812</t>
+          <t>216944</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>370818</t>
+          <t>368485</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>413054</t>
+          <t>416148</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,95%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>132538</t>
+          <t>129555</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>163890</t>
+          <t>161904</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>129991</t>
+          <t>131102</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>162502</t>
+          <t>162355</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>271021</t>
+          <t>270428</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>314186</t>
+          <t>315271</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>43,9%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11123</t>
+          <t>10884</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23640</t>
+          <t>24899</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7163</t>
+          <t>6901</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18623</t>
+          <t>18660</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>20803</t>
+          <t>20622</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>38279</t>
+          <t>38192</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5961</t>
+          <t>4629</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>3620</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5921</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7077,7 +7077,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -7100,12 +7100,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>661</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6289</t>
+          <t>5815</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4124</t>
+          <t>4740</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7619</t>
+          <t>7700</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07A08-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07A08-Edad-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse alegre, percibida por el adulto en 2007 (tasa de respuesta: 99,6%)</t>
+          <t>Menores según la frecuencia de sentirse alegre, percibida por el/la adulto/a [KIDSCREEN 20] en 2007 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>73505</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>64179</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>82213</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>51,94%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>45,35%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>58,1%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>69396</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>60673</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>79013</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>59826</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>77912</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>54,69%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>47,81%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>62,27%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>73505</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>64127</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>83282</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>51,94%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>130555</t>
+          <t>130018</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>157084</t>
+          <t>156354</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,25%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>62018</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>52517</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>71210</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>43,82%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>37,11%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>50,32%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>53406</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>44457</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>62298</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>45091</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>63701</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>42,09%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>35,04%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>49,09%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>62018</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>53250</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>70926</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>43,82%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>101708</t>
+          <t>102664</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>127779</t>
+          <t>128320</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,81%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5191</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1959</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9192</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3,67%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>6,5%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>3359</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1330</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7524</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1320</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>7391</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>2,65%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>5,93%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>5191</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2050</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>9274</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>3,67%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4649</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13925</t>
+          <t>14176</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -1061,107 +1061,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>802</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4218</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,98%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>802</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3230</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3990</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>802</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4020</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -1174,107 +1174,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>733</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4511</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4286</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,58%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>3,38%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>733</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>4424</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>733</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4049</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>126894</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>126894</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>126894</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>113648</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>102117</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>124381</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>55,69%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>50,04%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>60,95%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>151</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>102482</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>91757</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>115179</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>90784</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>114131</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>52,8%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>47,27%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>59,34%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>113648</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>101987</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>124997</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>55,69%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>198147</t>
+          <t>199604</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>231616</t>
+          <t>230907</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>57,99%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>77637</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>67119</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>89151</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>38,04%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>32,89%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>43,69%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>79848</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>67847</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>91023</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>68492</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>91922</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>41,14%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>34,96%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>46,9%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>77637</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>66573</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>88799</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>38,04%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>143417</t>
+          <t>142791</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>173755</t>
+          <t>173125</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,48%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>11295</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6644</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>17432</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>5,53%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>8,54%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>9754</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>5547</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>15027</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>5620</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>15172</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>5,03%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>7,74%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>11295</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>6539</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>17236</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>5,53%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14772</t>
+          <t>14616</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>29176</t>
+          <t>29044</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -1743,72 +1743,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1492</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5730</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,81%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>683</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3465</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3409</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,35%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1492</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5322</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>675</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5917</t>
+          <t>6171</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -1856,107 +1856,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>1329</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4429</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4033</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,68%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1329</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>4464</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1329</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>4009</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>204072</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>204072</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>204072</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>204072</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>204072</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>204072</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>187153</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>171952</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>202016</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>54,16%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>49,76%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>58,46%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>171878</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>157380</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>187675</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>158494</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>186093</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>53,55%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>49,03%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>58,47%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>187153</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>171764</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>201130</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>54,16%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>338003</t>
+          <t>338400</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>378401</t>
+          <t>378797</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>56,83%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>139655</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>124546</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>153196</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>40,41%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>36,04%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>44,33%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>133254</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>117367</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>148109</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>119334</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>146695</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>41,51%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>36,56%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>46,14%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>139655</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>125080</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>154784</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>40,41%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>253439</t>
+          <t>252055</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>294176</t>
+          <t>292945</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>43,95%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>16486</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>11268</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>24251</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>4,77%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>7,02%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>13113</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>8358</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>19198</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>8232</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>19115</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>4,09%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>5,98%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>16486</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>10637</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>23672</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>4,77%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>21278</t>
+          <t>21934</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>38267</t>
+          <t>38966</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -2425,74 +2425,74 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2293</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>6234</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>683</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3425</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3435</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,21%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>1,07%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>2293</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>682</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>6039</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>4</t>
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>688</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7854</t>
+          <t>7916</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -2538,72 +2538,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>2063</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5581</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5548</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,64%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>645</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5949</t>
+          <t>5510</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>345587</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>345587</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>345587</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>476</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>320991</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>320991</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>320991</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>345587</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>345587</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>345587</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2813,13 +2813,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse alegre, percibida por el adulto en 2012 (tasa de respuesta: 98,12%)</t>
+          <t>Menores según la frecuencia de sentirse alegre, percibida por el/la adulto/a [KIDSCREEN 20] en 2012 (tasa de respuesta: 98,12%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2830,7 +2830,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2998,72 +2998,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>86830</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>76655</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>96792</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>55,42%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>48,93%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>61,78%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>98337</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>88269</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>108282</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>88206</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>107224</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>63,52%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>57,01%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>69,94%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>86830</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>75764</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>96254</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>55,42%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>171187</t>
+          <t>170774</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>199100</t>
+          <t>199662</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>64,1%</t>
         </is>
       </c>
     </row>
@@ -3111,72 +3111,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>60868</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>51398</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>70588</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>38,85%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>32,81%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>45,05%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>52917</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>42877</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>62545</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>44051</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>63873</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>34,18%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>27,69%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>40,4%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60868</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>51328</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>71355</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>38,85%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99363</t>
+          <t>99411</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>128169</t>
+          <t>127284</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>40,86%</t>
         </is>
       </c>
     </row>
@@ -3224,74 +3224,74 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6916</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3476</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12109</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>4,41%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>7,73%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>2798</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>657</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7038</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>629</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>6823</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>1,81%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>6916</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>3449</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>11777</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>4,41%</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>7,52%</t>
-        </is>
-      </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>14</t>
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5426</t>
+          <t>5504</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15754</t>
+          <t>16076</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -3337,72 +3337,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1316</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4722</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>768</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3840</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3534</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,5%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1316</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4041</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>624</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5553</t>
+          <t>5752</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -3450,107 +3450,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4041</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>744</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3139</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>4164</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>744</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4440</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -3563,57 +3563,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>156674</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>156674</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>156674</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>154820</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>154820</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>154820</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>156674</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>156674</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>156674</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3680,72 +3680,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>101648</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>90277</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>110976</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>57,81%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>51,34%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>63,11%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>91841</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>81074</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>81557</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>102627</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>54,95%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>48,51%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>60,86%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>101648</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>91021</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>112932</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>57,81%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>178246</t>
+          <t>178277</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>207922</t>
+          <t>207895</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>60,62%</t>
         </is>
       </c>
     </row>
@@ -3793,72 +3793,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>66397</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>56967</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>78210</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>37,76%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>32,4%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>44,48%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>68036</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>58794</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>78645</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>57285</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>78307</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>40,71%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>35,18%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>47,06%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>66397</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>56448</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>76927</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>37,76%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>120750</t>
+          <t>119231</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>149409</t>
+          <t>149437</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,57%</t>
         </is>
       </c>
     </row>
@@ -3906,72 +3906,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5291</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2467</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>10618</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>6,04%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>5082</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2144</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>9990</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>9834</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>3,04%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,98%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>5291</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>2203</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>9894</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5891</t>
+          <t>5983</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17447</t>
+          <t>16715</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -4024,67 +4024,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>1204</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3692</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>1516</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5310</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4998</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,91%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,18%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1204</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4309</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>693</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6581</t>
+          <t>6435</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -4132,72 +4132,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1294</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4612</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3319</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3252</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,39%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1294</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4565</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>610</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5214</t>
+          <t>5308</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -4245,57 +4245,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>175834</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>175834</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>175834</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>167130</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>167130</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>167130</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>175834</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>175834</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>175834</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4362,107 +4362,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>188478</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>174244</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>200977</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>56,68%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>52,4%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>60,44%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>190178</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>176647</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>205297</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>175644</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>203893</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>59,07%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>54,87%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>63,77%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>188478</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>173078</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>202939</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>56,68%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
+          <t>63,33%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>378656</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>358565</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>399446</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>57,86%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>54,79%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>61,03%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>548</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>378656</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>357244</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>399052</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>57,86%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>54,59%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>60,97%</t>
         </is>
       </c>
     </row>
@@ -4475,72 +4475,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>127265</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>113764</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>142111</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>38,27%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>34,21%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>42,74%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>120953</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>106485</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>135861</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>107417</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>136276</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>37,57%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>33,07%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>42,2%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>127265</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>112876</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>141458</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>38,27%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>228213</t>
+          <t>229628</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>269308</t>
+          <t>269782</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,22%</t>
         </is>
       </c>
     </row>
@@ -4588,107 +4588,107 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>12207</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>7598</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>19282</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3,67%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>5,8%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>7880</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>4471</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>13748</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>4112</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>13846</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>2,45%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>4,3%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>20087</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>13756</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>27959</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>4,27%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>12207</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>7347</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>19014</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>3,67%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>5,72%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>20087</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>13449</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>28805</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>2,05%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
-        <is>
-          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -4701,72 +4701,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2520</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>5734</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>2283</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>691</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>6061</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>6131</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,71%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,21%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>2520</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>686</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>6229</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9660</t>
+          <t>9162</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -4814,72 +4814,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2039</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>5482</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3787</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3318</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>2039</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>611</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>6302</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>686</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6781</t>
+          <t>6771</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -4927,57 +4927,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>332508</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>332508</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>332508</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>457</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>321950</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>321950</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>321950</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>332508</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>332508</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>332508</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5089,13 +5089,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse alegre, percibida por el adulto en 2016 (tasa de respuesta: 99,02%)</t>
+          <t>Menores según la frecuencia de sentirse alegre, percibida por el/la adulto/a [KIDSCREEN 20] en 2016 (tasa de respuesta: 99,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5106,7 +5106,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5279,67 +5279,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>110391</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>99539</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>122734</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>58,93%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>53,14%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>65,52%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>106241</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>95255</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>117742</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>94587</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>117368</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>57,12%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>51,22%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>63,31%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>110391</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>98936</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>122419</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>58,93%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>200629</t>
+          <t>198114</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>231952</t>
+          <t>232100</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>62,18%</t>
         </is>
       </c>
     </row>
@@ -5387,72 +5387,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>70000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>58364</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>80681</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>37,37%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>31,16%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>43,07%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>73190</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>61222</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>83572</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>62608</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>84373</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>39,35%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>32,92%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>44,94%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>70000</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>58031</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>81596</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>37,37%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>126773</t>
+          <t>128108</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>159731</t>
+          <t>161243</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>43,19%</t>
         </is>
       </c>
     </row>
@@ -5500,72 +5500,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5552</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2681</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10410</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2,96%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>5,56%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>6552</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3327</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>11669</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>3479</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>11780</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>3,52%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>6,27%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>5552</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2697</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>10452</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>2,96%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7136</t>
+          <t>7511</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18223</t>
+          <t>19647</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -5726,107 +5726,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4739</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>1370</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>4914</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1370</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4437</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -5839,57 +5839,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>187313</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>187313</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>187313</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>267</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>185983</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>185983</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>185983</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>187313</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>187313</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>187313</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5961,67 +5961,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>90787</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>79761</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>102302</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>52,16%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>45,83%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>58,78%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>84175</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>73371</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>95495</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>73147</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>95088</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>49,29%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>42,96%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>55,91%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>90787</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>79330</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>101214</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>52,16%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>159459</t>
+          <t>159604</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>189934</t>
+          <t>190290</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>55,18%</t>
         </is>
       </c>
     </row>
@@ -6069,72 +6069,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>76300</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>64514</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>86983</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>43,84%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>37,07%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>49,98%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>73530</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>62290</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>83078</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>63534</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>84713</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>43,05%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>36,47%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>48,64%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>76300</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>65775</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>87603</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>43,84%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>135844</t>
+          <t>134137</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>166477</t>
+          <t>165901</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>48,11%</t>
         </is>
       </c>
     </row>
@@ -6182,72 +6182,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6244</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2782</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>11186</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3,59%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>6,43%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>9964</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>5602</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>16198</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>5660</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>16273</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>5,83%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>9,48%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>6244</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>2865</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>11428</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10901</t>
+          <t>10696</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>23520</t>
+          <t>24083</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -6300,102 +6300,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3568</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>993</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4795</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4921</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,58%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,81%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>717</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1710</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4278</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>6469</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>6205</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -6408,72 +6408,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>2128</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5775</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>6097</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>1,25%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,38%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>661</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6262</t>
+          <t>6261</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6521,57 +6521,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>170789</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>170789</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>170789</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6643,67 +6643,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>201178</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>184612</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>217591</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>55,67%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>51,09%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>60,21%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>190417</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>173862</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>207589</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>174796</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>207005</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>53,37%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>48,73%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>58,19%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>201178</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>185167</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>216944</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>55,67%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>368485</t>
+          <t>367057</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>416148</t>
+          <t>413429</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>57,57%</t>
         </is>
       </c>
     </row>
@@ -6751,72 +6751,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>146300</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>131269</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>164127</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>40,49%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>36,33%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>45,42%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>208</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>146720</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>129555</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>161904</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>130623</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>162286</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>41,12%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>36,31%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>45,38%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>146300</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>131102</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>162355</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>40,49%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>270428</t>
+          <t>272134</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>315271</t>
+          <t>316863</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>44,12%</t>
         </is>
       </c>
     </row>
@@ -6864,72 +6864,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>11796</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>7207</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>18543</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>5,13%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>16515</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>10884</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>24899</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>10500</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>23544</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>4,63%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>6,98%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>11796</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>6901</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>18660</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>3,26%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>20622</t>
+          <t>20541</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>38192</t>
+          <t>37598</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -6982,102 +6982,102 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3595</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
           <t>993</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4629</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4972</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,28%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>717</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1710</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3620</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>6203</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>6008</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -7090,107 +7090,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>5359</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>2128</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>661</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5815</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>660</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5718</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,6%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>3498</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>1374</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>7891</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1370</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>4740</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>3498</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>1361</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>7700</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -7203,57 +7203,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>496</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>361361</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>361361</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>361361</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>510</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>356772</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>356772</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>356772</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>496</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>361361</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>361361</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>361361</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
